--- a/dadosConnepi.xlsx
+++ b/dadosConnepi.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b7beb5d6fee94c27/Documents/meusCursos/regressao-connepi2024Local/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b7beb5d6fee94c27/Documents/meusCursos/regressao-connepi2024/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="11_94B1572A54DEAC0FFB039038BE0E4ED8A2FF9F7C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33A7F277-941C-48E2-912B-89F4EB376EBC}"/>
+  <xr:revisionPtr revIDLastSave="90" documentId="11_94B1572A54DEAC0FFB039038BE0E4ED8A2FF9F7C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7515597C-7077-493A-807E-EFB547772CD2}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ex1_compressao" sheetId="1" r:id="rId1"/>
+    <sheet name="ex1_compressao" sheetId="3" r:id="rId1"/>
     <sheet name="ex2_fabrica" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -392,7 +392,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FDCCD4E-B591-4C54-9CCA-B571F8C21A6C}">
   <dimension ref="A1:B16"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -409,7 +409,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>9.44</v>
+        <v>9.4499999999999993</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -417,7 +417,7 @@
         <v>0</v>
       </c>
       <c r="B3">
-        <v>9.77</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -425,7 +425,7 @@
         <v>0</v>
       </c>
       <c r="B4">
-        <v>11.56</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -433,7 +433,7 @@
         <v>0</v>
       </c>
       <c r="B5">
-        <v>10.07</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -441,7 +441,7 @@
         <v>0</v>
       </c>
       <c r="B6">
-        <v>10.130000000000001</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -449,7 +449,7 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>8.7200000000000006</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -457,7 +457,7 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>7.46</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -465,7 +465,7 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>5.73</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -473,7 +473,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>6.31</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -481,7 +481,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>6.55</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -489,7 +489,7 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>5.22</v>
+        <v>5.0999999999999996</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -497,7 +497,7 @@
         <v>20</v>
       </c>
       <c r="B13">
-        <v>4.3600000000000003</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -505,7 +505,7 @@
         <v>20</v>
       </c>
       <c r="B14">
-        <v>4.4000000000000004</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
@@ -513,7 +513,7 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>4.1100000000000003</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -521,7 +521,7 @@
         <v>20</v>
       </c>
       <c r="B16">
-        <v>3.44</v>
+        <v>3.9</v>
       </c>
     </row>
   </sheetData>
